--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU7"/>
+  <dimension ref="A1:AU8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -721,68 +721,68 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -828,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="AU2" s="3" t="n">
-        <v>46203.5</v>
+        <v>46203.29166666666</v>
       </c>
     </row>
     <row r="3">
@@ -837,7 +837,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -987,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="AU3" s="3" t="n">
-        <v>46203.54166666666</v>
+        <v>46203.5</v>
       </c>
     </row>
     <row r="4">
@@ -996,12 +996,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="AU4" s="3" t="n">
-        <v>46203.8125</v>
+        <v>46203.54166666666</v>
       </c>
     </row>
     <row r="5">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="AU5" s="3" t="n">
-        <v>46203.83333333334</v>
+        <v>46203.8125</v>
       </c>
     </row>
     <row r="6">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="AU6" s="3" t="n">
-        <v>46203.85416666666</v>
+        <v>46203.83333333334</v>
       </c>
     </row>
     <row r="7">
@@ -1488,141 +1488,300 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="3" t="n">
+        <v>46203.85416666666</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Botafogo PB</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Brusque</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="inlineStr">
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" s="3" t="n">
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="3" t="n">
         <v>46203.85416666666</v>
       </c>
     </row>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>6.59</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="O7" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>3.32</v>
+        <v>3.91</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="O8" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P8" t="n">
-        <v>3.91</v>
+        <v>3.32</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>3.91</v>
+        <v>3.32</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>3.32</v>
+        <v>3.91</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -893,10 +893,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -905,43 +905,43 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="O7" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>3.32</v>
+        <v>3.91</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="O8" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P8" t="n">
-        <v>3.91</v>
+        <v>3.32</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -1211,55 +1211,55 @@
         <v>6.59</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1529,55 +1529,55 @@
         <v>3.32</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1688,55 +1688,55 @@
         <v>3.91</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -893,55 +893,55 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="R3" t="n">
         <v>2.75</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U3" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="V3" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W3" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1052,55 +1052,55 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,77 +1520,77 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="O7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U7" t="n">
         <v>3.2</v>
       </c>
-      <c r="P7" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="V7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y7" t="n">
         <v>1.41</v>
       </c>
-      <c r="T7" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="V7" t="n">
+      <c r="Z7" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.36</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.24</v>
       </c>
       <c r="AK7" t="n">
         <v>1.67</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AA8" t="n">
         <v>2.02</v>
       </c>
-      <c r="O8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="AB8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.3</v>
       </c>
-      <c r="W8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X8" t="n">
+      <c r="AE8" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AF8" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
         <v>1.67</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AA7" t="n">
         <v>2.02</v>
       </c>
-      <c r="O7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V7" t="n">
+      <c r="AB7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.3</v>
       </c>
-      <c r="W7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X7" t="n">
+      <c r="AE7" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AF7" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AK7" t="n">
         <v>1.67</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,77 +1679,77 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="O8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U8" t="n">
         <v>3.2</v>
       </c>
-      <c r="P8" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="V8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1.41</v>
       </c>
-      <c r="T8" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="Z8" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.36</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
         <v>1.67</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -728,49 +728,49 @@
         <v>2.31</v>
       </c>
       <c r="O2" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P2" t="n">
         <v>2.57</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S2" t="n">
         <v>1.25</v>
       </c>
       <c r="T2" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="U2" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="V2" t="n">
         <v>1.57</v>
       </c>
       <c r="W2" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z2" t="n">
         <v>4.55</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="AD2" t="n">
         <v>1.53</v>
@@ -779,26 +779,26 @@
         <v>1.18</v>
       </c>
       <c r="AF2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
         <v>1.44</v>
       </c>
-      <c r="AG2" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AK2" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q3" t="n">
         <v>1.64</v>
@@ -929,7 +929,7 @@
         <v>2.62</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AD3" t="n">
         <v>1.57</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="Q4" t="n">
         <v>1.78</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,77 +1520,77 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="O7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U7" t="n">
         <v>3.2</v>
       </c>
-      <c r="P7" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="V7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y7" t="n">
         <v>1.41</v>
       </c>
-      <c r="T7" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="V7" t="n">
+      <c r="Z7" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.36</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.24</v>
       </c>
       <c r="AK7" t="n">
         <v>1.67</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AA8" t="n">
         <v>2.02</v>
       </c>
-      <c r="O8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="AB8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.3</v>
       </c>
-      <c r="W8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X8" t="n">
+      <c r="AE8" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AF8" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
         <v>1.67</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,77 +1520,77 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="O7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U7" t="n">
         <v>3.2</v>
       </c>
-      <c r="P7" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="V7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y7" t="n">
         <v>1.41</v>
       </c>
-      <c r="T7" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="V7" t="n">
+      <c r="Z7" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.36</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.24</v>
       </c>
       <c r="AK7" t="n">
         <v>1.67</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AA8" t="n">
         <v>2.02</v>
       </c>
-      <c r="O8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="AB8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.3</v>
       </c>
-      <c r="W8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X8" t="n">
+      <c r="AE8" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AF8" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
         <v>1.67</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="O2" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P2" t="n">
         <v>2.57</v>
@@ -767,7 +767,7 @@
         <v>1.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AC2" t="n">
         <v>2.5</v>
@@ -893,55 +893,55 @@
         <v>8.949999999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="R3" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="S3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T3" t="n">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="U3" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V3" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W3" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
       <c r="AA3" t="n">
         <v>1.44</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,19 +1043,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="O4" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="P4" t="n">
-        <v>7.55</v>
+        <v>6</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="S4" t="n">
         <v>1.2</v>
@@ -1064,10 +1064,10 @@
         <v>4</v>
       </c>
       <c r="U4" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W4" t="n">
         <v>1.17</v>
@@ -1076,31 +1076,31 @@
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AK4" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="O5" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="P5" t="n">
-        <v>6.59</v>
+        <v>5.65</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T5" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="U5" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="V5" t="n">
         <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.98</v>
+        <v>2.13</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="P7" t="n">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="S7" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.44</v>
+        <v>2.27</v>
       </c>
       <c r="U7" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="V7" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.69</v>
+        <v>2.43</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.43</v>
+        <v>2.52</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.16</v>
+        <v>1.93</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P8" t="n">
-        <v>3.32</v>
+        <v>3.55</v>
       </c>
       <c r="Q8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T8" t="n">
         <v>2.63</v>
       </c>
-      <c r="R8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.72</v>
-      </c>
       <c r="U8" t="n">
-        <v>2.92</v>
+        <v>3.07</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="AA8" t="n">
         <v>2.02</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.15</v>
+        <v>3.58</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -728,7 +728,7 @@
         <v>2.3</v>
       </c>
       <c r="O2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P2" t="n">
         <v>2.57</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -728,10 +728,10 @@
         <v>2.3</v>
       </c>
       <c r="O2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P2" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="Q2" t="n">
         <v>2.77</v>
@@ -893,7 +893,7 @@
         <v>8.949999999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="R3" t="n">
         <v>2.7</v>
@@ -917,31 +917,31 @@
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.95</v>
+        <v>4.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1049,7 +1049,7 @@
         <v>4.6</v>
       </c>
       <c r="P4" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="Q4" t="n">
         <v>1.77</v>
@@ -1061,43 +1061,43 @@
         <v>1.2</v>
       </c>
       <c r="T4" t="n">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="U4" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="V4" t="n">
         <v>1.63</v>
       </c>
       <c r="W4" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AA4" t="n">
         <v>1.41</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="AC4" t="n">
         <v>2.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG4" t="n">
         <v>2</v>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AK4" t="n">
         <v>2.78</v>
@@ -1275,7 +1275,7 @@
         <v>1.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1529,19 +1529,19 @@
         <v>4.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="T7" t="n">
         <v>2.27</v>
       </c>
       <c r="U7" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="V7" t="n">
         <v>1.22</v>
@@ -1550,19 +1550,19 @@
         <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
         <v>1.44</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="AA7" t="n">
         <v>2.52</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AC7" t="n">
         <v>4.9</v>
@@ -1577,7 +1577,7 @@
         <v>2.11</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1706,7 +1706,7 @@
         <v>1.31</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>
@@ -1715,22 +1715,22 @@
         <v>1.29</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="AA8" t="n">
         <v>2.02</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.58</v>
+        <v>3.15</v>
       </c>
       <c r="AD8" t="n">
         <v>1.21</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF8" t="n">
         <v>1.82</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -1217,10 +1217,10 @@
         <v>2.08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="T5" t="n">
-        <v>2.42</v>
+        <v>2.63</v>
       </c>
       <c r="U5" t="n">
         <v>3.25</v>
@@ -1244,7 +1244,7 @@
         <v>2.19</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC5" t="n">
         <v>4.1</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="O7" t="n">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="P7" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S7" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="T7" t="n">
-        <v>2.27</v>
+        <v>2.63</v>
       </c>
       <c r="U7" t="n">
-        <v>3.5</v>
+        <v>3.07</v>
       </c>
       <c r="V7" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.35</v>
+        <v>3.02</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.52</v>
+        <v>2.01</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.9</v>
+        <v>3.15</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.11</v>
+        <v>1.82</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AK7" t="n">
         <v>1.7</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="O8" t="n">
-        <v>3.15</v>
+        <v>2.55</v>
       </c>
       <c r="P8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U8" t="n">
         <v>3.55</v>
       </c>
-      <c r="Q8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.07</v>
-      </c>
       <c r="V8" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X8" t="n">
         <v>1.06</v>
       </c>
-      <c r="X8" t="n">
-        <v>1</v>
-      </c>
       <c r="Y8" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.02</v>
+        <v>2.35</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.02</v>
+        <v>2.52</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.15</v>
+        <v>4.85</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.82</v>
+        <v>2.09</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK8" t="n">
         <v>1.7</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -1211,28 +1211,28 @@
         <v>5.65</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="R5" t="n">
         <v>2.08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="T5" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="U5" t="n">
         <v>3.25</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
         <v>1.43</v>
@@ -1256,10 +1256,10 @@
         <v>1.01</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1559,10 +1559,10 @@
         <v>3.02</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC7" t="n">
         <v>3.15</v>
@@ -1694,28 +1694,28 @@
         <v>1.88</v>
       </c>
       <c r="S8" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="T8" t="n">
         <v>2.27</v>
       </c>
       <c r="U8" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="V8" t="n">
         <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
         <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="AA8" t="n">
         <v>2.52</v>
@@ -1724,7 +1724,7 @@
         <v>1.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="AD8" t="n">
         <v>1.13</v>
@@ -1733,7 +1733,7 @@
         <v>1.02</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AG8" t="n">
         <v>1.67</v>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -1202,37 +1202,37 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="O5" t="n">
-        <v>3.15</v>
+        <v>3.64</v>
       </c>
       <c r="P5" t="n">
-        <v>5.65</v>
+        <v>6.09</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="R5" t="n">
         <v>2.08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="U5" t="n">
-        <v>3.25</v>
+        <v>2.91</v>
       </c>
       <c r="V5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W5" t="n">
         <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
         <v>1.43</v>
@@ -1241,16 +1241,16 @@
         <v>2.55</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AB5" t="n">
         <v>1.61</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.1</v>
+        <v>3.98</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE5" t="n">
         <v>1.01</v>
@@ -1259,7 +1259,7 @@
         <v>2.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="O7" t="n">
         <v>3.15</v>
       </c>
       <c r="P7" t="n">
-        <v>3.55</v>
+        <v>3.72</v>
       </c>
       <c r="Q7" t="n">
         <v>2.6</v>
@@ -1535,49 +1535,49 @@
         <v>2.05</v>
       </c>
       <c r="S7" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T7" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="U7" t="n">
-        <v>3.07</v>
+        <v>2.91</v>
       </c>
       <c r="V7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W7" t="n">
         <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AC7" t="n">
         <v>3.15</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="O8" t="n">
-        <v>2.55</v>
+        <v>3.06</v>
       </c>
       <c r="P8" t="n">
-        <v>4.1</v>
+        <v>3.86</v>
       </c>
       <c r="Q8" t="n">
         <v>2.5</v>
@@ -1715,7 +1715,7 @@
         <v>1.44</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="AA8" t="n">
         <v>2.52</v>
@@ -1730,7 +1730,7 @@
         <v>1.13</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF8" t="n">
         <v>2.11</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="O2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P2" t="n">
         <v>2.5</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="O2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P2" t="n">
         <v>2.5</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R7" t="n">
         <v>1.88</v>
       </c>
-      <c r="O7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.05</v>
-      </c>
       <c r="S7" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.56</v>
+        <v>2.27</v>
       </c>
       <c r="U7" t="n">
-        <v>2.91</v>
+        <v>3.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X7" t="n">
         <v>1.06</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AF7" t="n">
-        <v>1.68</v>
+        <v>2.11</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="O8" t="n">
-        <v>3.06</v>
+        <v>3.15</v>
       </c>
       <c r="P8" t="n">
-        <v>3.86</v>
+        <v>3.72</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="T8" t="n">
-        <v>2.27</v>
+        <v>2.56</v>
       </c>
       <c r="U8" t="n">
-        <v>3.5</v>
+        <v>2.91</v>
       </c>
       <c r="V8" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.35</v>
+        <v>2.85</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.9</v>
+        <v>3.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.11</v>
+        <v>1.68</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -1211,13 +1211,13 @@
         <v>6.09</v>
       </c>
       <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
         <v>2.1</v>
       </c>
-      <c r="R5" t="n">
-        <v>2.08</v>
-      </c>
       <c r="S5" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T5" t="n">
         <v>2.62</v>
@@ -1229,31 +1229,31 @@
         <v>1.28</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="AD5" t="n">
         <v>1.17</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF5" t="n">
         <v>2.1</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1550,19 +1550,19 @@
         <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
         <v>1.44</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="AA7" t="n">
         <v>2.52</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AC7" t="n">
         <v>4.9</v>
@@ -1571,7 +1571,7 @@
         <v>1.13</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF7" t="n">
         <v>2.11</v>
@@ -1685,7 +1685,7 @@
         <v>3.15</v>
       </c>
       <c r="P8" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="Q8" t="n">
         <v>2.6</v>
@@ -1694,7 +1694,7 @@
         <v>2.05</v>
       </c>
       <c r="S8" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="T8" t="n">
         <v>2.56</v>
@@ -1703,10 +1703,10 @@
         <v>2.91</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
@@ -1715,28 +1715,28 @@
         <v>1.32</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -908,7 +908,7 @@
         <v>2.16</v>
       </c>
       <c r="V3" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W3" t="n">
         <v>1.12</v>
@@ -1061,10 +1061,10 @@
         <v>1.2</v>
       </c>
       <c r="T4" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="U4" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="V4" t="n">
         <v>1.63</v>
@@ -1076,22 +1076,22 @@
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z4" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AA4" t="n">
         <v>1.41</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="AC4" t="n">
         <v>2.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AE4" t="n">
         <v>1.24</v>
@@ -1100,7 +1100,7 @@
         <v>1.67</v>
       </c>
       <c r="AG4" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>1.09</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1208,16 +1208,16 @@
         <v>3.64</v>
       </c>
       <c r="P5" t="n">
-        <v>6.09</v>
+        <v>6.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T5" t="n">
         <v>2.62</v>
@@ -1244,7 +1244,7 @@
         <v>2.14</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AC5" t="n">
         <v>3.95</v>
@@ -1259,7 +1259,7 @@
         <v>2.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="O6" t="n">
-        <v>3.13</v>
+        <v>2.73</v>
       </c>
       <c r="P6" t="n">
-        <v>3.12</v>
+        <v>3.54</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="O7" t="n">
-        <v>3.06</v>
+        <v>3.25</v>
       </c>
       <c r="P7" t="n">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="T7" t="n">
-        <v>2.27</v>
+        <v>2.75</v>
       </c>
       <c r="U7" t="n">
-        <v>3.5</v>
+        <v>2.91</v>
       </c>
       <c r="V7" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="W7" t="n">
         <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.11</v>
+        <v>1.78</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="O8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P8" t="n">
-        <v>3.7</v>
+        <v>4.69</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="R8" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="S8" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="T8" t="n">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="U8" t="n">
-        <v>2.91</v>
+        <v>3.58</v>
       </c>
       <c r="V8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W8" t="n">
         <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.1</v>
+        <v>2.49</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.78</v>
+        <v>2.11</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -1211,13 +1211,13 @@
         <v>6.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="R5" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="S5" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="T5" t="n">
         <v>2.62</v>
@@ -1229,10 +1229,10 @@
         <v>1.28</v>
       </c>
       <c r="W5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X5" t="n">
         <v>1.05</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
         <v>1.38</v>
@@ -1253,7 +1253,7 @@
         <v>1.17</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF5" t="n">
         <v>2.1</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1409,10 +1409,10 @@
         <v>4.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF6" t="n">
         <v>1.93</v>
@@ -1526,7 +1526,7 @@
         <v>3.25</v>
       </c>
       <c r="P7" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Q7" t="n">
         <v>2.6</v>
@@ -1547,7 +1547,7 @@
         <v>1.29</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
         <v>1.05</v>
@@ -1577,7 +1577,7 @@
         <v>1.78</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1679,25 +1679,25 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="P8" t="n">
-        <v>4.69</v>
+        <v>4.85</v>
       </c>
       <c r="Q8" t="n">
         <v>2.45</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="S8" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="U8" t="n">
         <v>3.58</v>
@@ -1715,13 +1715,13 @@
         <v>1.44</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="AA8" t="n">
         <v>2.49</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AC8" t="n">
         <v>4.9</v>
@@ -1733,7 +1733,7 @@
         <v>1.02</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="AG8" t="n">
         <v>1.6</v>
@@ -1752,7 +1752,7 @@
         <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="O5" t="n">
-        <v>3.64</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>6.2</v>
+        <v>6.09</v>
       </c>
       <c r="Q5" t="n">
         <v>2.25</v>
@@ -1232,7 +1232,7 @@
         <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
         <v>1.38</v>
@@ -1253,13 +1253,13 @@
         <v>1.17</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF5" t="n">
         <v>2.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1364,61 +1364,61 @@
         <v>2.25</v>
       </c>
       <c r="O6" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="P6" t="n">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S6" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="T6" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="U6" t="n">
         <v>3.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
         <v>1.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AB6" t="n">
         <v>1.53</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF6" t="n">
         <v>1.93</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R7" t="n">
         <v>1.9</v>
       </c>
-      <c r="O7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.05</v>
-      </c>
       <c r="S7" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.75</v>
+        <v>2.31</v>
       </c>
       <c r="U7" t="n">
-        <v>2.91</v>
+        <v>3.55</v>
       </c>
       <c r="V7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.1</v>
+        <v>2.49</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.4</v>
+        <v>4.85</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.78</v>
+        <v>2.22</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="O8" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="P8" t="n">
-        <v>4.85</v>
+        <v>3.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="T8" t="n">
-        <v>2.24</v>
+        <v>2.75</v>
       </c>
       <c r="U8" t="n">
-        <v>3.58</v>
+        <v>2.91</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X8" t="n">
         <v>1.05</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.09</v>
-      </c>
       <c r="Y8" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.49</v>
+        <v>2.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AE8" t="n">
         <v>1.02</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.24</v>
+        <v>1.78</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="O7" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="P7" t="n">
-        <v>4.79</v>
+        <v>3.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="T7" t="n">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="U7" t="n">
-        <v>3.55</v>
+        <v>2.91</v>
       </c>
       <c r="V7" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X7" t="n">
         <v>1.05</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y7" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.49</v>
+        <v>2.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.85</v>
+        <v>3.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.22</v>
+        <v>1.78</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="O8" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="P8" t="n">
-        <v>3.7</v>
+        <v>4.79</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="R8" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="S8" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.75</v>
+        <v>2.31</v>
       </c>
       <c r="U8" t="n">
-        <v>2.91</v>
+        <v>3.55</v>
       </c>
       <c r="V8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.1</v>
+        <v>2.49</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.4</v>
+        <v>4.85</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.78</v>
+        <v>2.22</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -908,7 +908,7 @@
         <v>2.16</v>
       </c>
       <c r="V3" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W3" t="n">
         <v>1.12</v>
@@ -917,25 +917,25 @@
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB3" t="n">
         <v>2.43</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF3" t="n">
         <v>1.76</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1049,10 +1049,10 @@
         <v>4.6</v>
       </c>
       <c r="P4" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="R4" t="n">
         <v>2.61</v>
@@ -1082,16 +1082,16 @@
         <v>5.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="AC4" t="n">
         <v>2.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AE4" t="n">
         <v>1.24</v>
@@ -1116,7 +1116,7 @@
         <v>1.09</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>6.09</v>
+        <v>5.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S5" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="T5" t="n">
         <v>2.62</v>
@@ -1229,10 +1229,10 @@
         <v>1.28</v>
       </c>
       <c r="W5" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
         <v>1.38</v>
@@ -1253,13 +1253,13 @@
         <v>1.17</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF5" t="n">
         <v>2.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1364,10 +1364,10 @@
         <v>2.25</v>
       </c>
       <c r="O6" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="P6" t="n">
-        <v>3.1</v>
+        <v>3.66</v>
       </c>
       <c r="Q6" t="n">
         <v>2.74</v>
@@ -1376,49 +1376,49 @@
         <v>1.91</v>
       </c>
       <c r="S6" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="U6" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="V6" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE6" t="n">
         <v>1.05</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="O7" t="n">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="P7" t="n">
-        <v>3.7</v>
+        <v>5.13</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="R7" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S7" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.75</v>
+        <v>2.31</v>
       </c>
       <c r="U7" t="n">
-        <v>2.91</v>
+        <v>3.55</v>
       </c>
       <c r="V7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.88</v>
+        <v>2.41</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.1</v>
+        <v>2.49</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.4</v>
+        <v>4.85</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.78</v>
+        <v>2.22</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="O8" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="P8" t="n">
-        <v>4.79</v>
+        <v>3.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="T8" t="n">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="U8" t="n">
-        <v>3.55</v>
+        <v>3.13</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AF8" t="n">
-        <v>2.22</v>
+        <v>1.91</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="O2" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P2" t="n">
         <v>2.5</v>
@@ -767,7 +767,7 @@
         <v>1.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AC2" t="n">
         <v>2.5</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="O7" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q7" t="n">
         <v>2.6</v>
       </c>
-      <c r="P7" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.45</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="T7" t="n">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="U7" t="n">
-        <v>3.55</v>
+        <v>3.13</v>
       </c>
       <c r="V7" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.41</v>
+        <v>3.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.49</v>
+        <v>2.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.85</v>
+        <v>4.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AE7" t="n">
         <v>1.04</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.22</v>
+        <v>1.91</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="O8" t="n">
-        <v>3.24</v>
+        <v>2.6</v>
       </c>
       <c r="P8" t="n">
-        <v>3.6</v>
+        <v>5.13</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="R8" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S8" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.75</v>
+        <v>2.31</v>
       </c>
       <c r="U8" t="n">
-        <v>3.13</v>
+        <v>3.55</v>
       </c>
       <c r="V8" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.1</v>
+        <v>2.41</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.1</v>
+        <v>2.49</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.1</v>
+        <v>4.85</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AE8" t="n">
         <v>1.04</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.91</v>
+        <v>2.22</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="O7" t="n">
-        <v>3.24</v>
+        <v>2.6</v>
       </c>
       <c r="P7" t="n">
-        <v>3.6</v>
+        <v>5.13</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="R7" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S7" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.75</v>
+        <v>2.31</v>
       </c>
       <c r="U7" t="n">
-        <v>3.13</v>
+        <v>3.55</v>
       </c>
       <c r="V7" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.1</v>
+        <v>2.41</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.1</v>
+        <v>2.49</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.1</v>
+        <v>4.85</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AE7" t="n">
         <v>1.04</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.91</v>
+        <v>2.22</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="O8" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q8" t="n">
         <v>2.6</v>
       </c>
-      <c r="P8" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.45</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="T8" t="n">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="U8" t="n">
-        <v>3.55</v>
+        <v>3.13</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.41</v>
+        <v>3.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.49</v>
+        <v>2.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.85</v>
+        <v>4.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AE8" t="n">
         <v>1.04</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.22</v>
+        <v>1.91</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="P3" t="n">
-        <v>8.949999999999999</v>
+        <v>8</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="S3" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T3" t="n">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="U3" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="V3" t="n">
         <v>1.62</v>
       </c>
       <c r="W3" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,25 +1043,25 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="O4" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>6</v>
+        <v>6.43</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="R4" t="n">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="S4" t="n">
         <v>1.2</v>
       </c>
       <c r="T4" t="n">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="U4" t="n">
         <v>2.11</v>
@@ -1070,37 +1070,37 @@
         <v>1.63</v>
       </c>
       <c r="W4" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
         <v>1.09</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AC4" t="n">
         <v>2.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="O5" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>5.67</v>
+        <v>6.35</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S5" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T5" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="U5" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="V5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="O7" t="n">
-        <v>2.6</v>
+        <v>3.16</v>
       </c>
       <c r="P7" t="n">
-        <v>5.13</v>
+        <v>4.55</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="R7" t="n">
         <v>1.95</v>
@@ -1538,16 +1538,16 @@
         <v>1.5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="U7" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
         <v>1.09</v>
@@ -1556,28 +1556,28 @@
         <v>1.44</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.49</v>
+        <v>2.53</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AE7" t="n">
         <v>1.04</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,61 +1679,61 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="O8" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="Q8" t="n">
         <v>2.6</v>
       </c>
       <c r="R8" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="T8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U8" t="n">
         <v>2.75</v>
       </c>
-      <c r="U8" t="n">
-        <v>3.13</v>
-      </c>
       <c r="V8" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
         <v>1.32</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AA8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF8" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.91</v>
       </c>
       <c r="AG8" t="n">
         <v>1.8</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="O2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P2" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="R2" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S2" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="T2" t="n">
-        <v>3.5</v>
+        <v>3.09</v>
       </c>
       <c r="U2" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="V2" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.55</v>
+        <v>3.85</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AB2" t="n">
         <v>2.3</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.46</v>
+        <v>2.18</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1367,19 +1367,19 @@
         <v>2.73</v>
       </c>
       <c r="P6" t="n">
-        <v>3.66</v>
+        <v>3.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.74</v>
+        <v>3.12</v>
       </c>
       <c r="R6" t="n">
         <v>1.91</v>
       </c>
       <c r="S6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="T6" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="U6" t="n">
         <v>3.22</v>
@@ -1391,34 +1391,34 @@
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
         <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -1361,16 +1361,16 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="O6" t="n">
         <v>2.73</v>
       </c>
       <c r="P6" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="R6" t="n">
         <v>1.91</v>
@@ -1382,10 +1382,10 @@
         <v>2.6</v>
       </c>
       <c r="U6" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
@@ -1415,7 +1415,7 @@
         <v>1.03</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG6" t="n">
         <v>1.75</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -1361,61 +1361,61 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="O6" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="P6" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
         <v>1.91</v>
       </c>
       <c r="S6" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="T6" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="U6" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="V6" t="n">
         <v>1.29</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
         <v>2.88</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.4</v>
+        <v>3.86</v>
       </c>
       <c r="AD6" t="n">
         <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AG6" t="n">
         <v>1.75</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="O7" t="n">
-        <v>3.16</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>4.55</v>
+        <v>3.57</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="T7" t="n">
         <v>2.35</v>
       </c>
       <c r="U7" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="V7" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="W7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X7" t="n">
         <v>1.02</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.09</v>
-      </c>
       <c r="Y7" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.53</v>
+        <v>2.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.9</v>
+        <v>4.33</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R8" t="n">
         <v>1.95</v>
       </c>
-      <c r="O8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
       <c r="S8" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="T8" t="n">
         <v>2.35</v>
       </c>
       <c r="U8" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.25</v>
+        <v>2.53</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.33</v>
+        <v>4.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -1202,28 +1202,28 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="O5" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P5" t="n">
-        <v>6.35</v>
+        <v>6.17</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="R5" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T5" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="U5" t="n">
-        <v>2.87</v>
+        <v>3.06</v>
       </c>
       <c r="V5" t="n">
         <v>1.3</v>
@@ -1232,7 +1232,7 @@
         <v>1.07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
         <v>1.31</v>
@@ -1244,7 +1244,7 @@
         <v>2.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC5" t="n">
         <v>3.8</v>
@@ -1259,7 +1259,7 @@
         <v>2.13</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="O7" t="n">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="P7" t="n">
-        <v>3.57</v>
+        <v>4.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="S7" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="T7" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="U7" t="n">
-        <v>2.75</v>
+        <v>3.78</v>
       </c>
       <c r="V7" t="n">
-        <v>1.38</v>
+        <v>1.19</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.25</v>
+        <v>2.73</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.33</v>
+        <v>5.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,61 +1679,61 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="O8" t="n">
-        <v>3.16</v>
+        <v>2.95</v>
       </c>
       <c r="P8" t="n">
-        <v>4.55</v>
+        <v>3.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="R8" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="T8" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="U8" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="V8" t="n">
         <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG8" t="n">
         <v>1.62</v>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -725,25 +725,25 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="O2" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="S2" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T2" t="n">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
       <c r="U2" t="n">
         <v>2.63</v>
@@ -761,28 +761,28 @@
         <v>1.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="AC2" t="n">
         <v>2.75</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF2" t="n">
         <v>1.6</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AK2" t="n">
         <v>1.55</v>
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="O3" t="n">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="P3" t="n">
-        <v>8</v>
+        <v>12.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="R3" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T3" t="n">
-        <v>3.68</v>
+        <v>3.88</v>
       </c>
       <c r="U3" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X3" t="n">
         <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.49</v>
+        <v>2.66</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="O4" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="P4" t="n">
-        <v>6.43</v>
+        <v>7.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="R4" t="n">
         <v>2.7</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T4" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="U4" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="V4" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="W4" t="n">
         <v>1.17</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>1.1</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1217,13 +1217,13 @@
         <v>2.08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T5" t="n">
         <v>2.62</v>
       </c>
       <c r="U5" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="V5" t="n">
         <v>1.3</v>
@@ -1361,61 +1361,61 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="O6" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R6" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="S6" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="T6" t="n">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="U6" t="n">
-        <v>3.22</v>
+        <v>2.95</v>
       </c>
       <c r="V6" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AB6" t="n">
         <v>1.53</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.86</v>
+        <v>3.34</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AG6" t="n">
         <v>1.75</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R7" t="n">
         <v>1.9</v>
       </c>
-      <c r="O7" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="P7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.85</v>
-      </c>
       <c r="S7" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="T7" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="U7" t="n">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="V7" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.73</v>
+        <v>2.55</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.06</v>
+        <v>1.88</v>
       </c>
       <c r="O8" t="n">
-        <v>2.95</v>
+        <v>2.78</v>
       </c>
       <c r="P8" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="R8" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="S8" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="T8" t="n">
         <v>2.19</v>
       </c>
       <c r="U8" t="n">
-        <v>3.9</v>
+        <v>3.78</v>
       </c>
       <c r="V8" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -717,42 +717,42 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="O2" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P2" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="R2" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T2" t="n">
-        <v>3.04</v>
+        <v>3.12</v>
       </c>
       <c r="U2" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W2" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X2" t="n">
         <v>1.03</v>
@@ -764,25 +764,25 @@
         <v>3.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AC2" t="n">
         <v>2.75</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF2" t="n">
         <v>1.6</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -791,41 +791,41 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46203.29166666666</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,65 +1520,65 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="O7" t="n">
-        <v>2.95</v>
+        <v>2.78</v>
       </c>
       <c r="P7" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="S7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.52</v>
       </c>
-      <c r="T7" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="O8" t="n">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="P8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC8" t="n">
         <v>5</v>
       </c>
-      <c r="Q8" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AD8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-30.xlsx
+++ b/jogos_2026-06-30.xlsx
@@ -861,96 +861,96 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="O3" t="n">
         <v>6.5</v>
       </c>
       <c r="P3" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="R3" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="S3" t="n">
         <v>1.22</v>
       </c>
       <c r="T3" t="n">
-        <v>3.88</v>
+        <v>3.98</v>
       </c>
       <c r="U3" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
         <v>1.09</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.6</v>
+        <v>5.85</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20', '54', '62']</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AJ3" t="n">
@@ -963,28 +963,28 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46203.5</v>
@@ -1043,52 +1043,52 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="O4" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="P4" t="n">
-        <v>7.75</v>
+        <v>6.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="S4" t="n">
         <v>1.22</v>
       </c>
       <c r="T4" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U4" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="V4" t="n">
         <v>1.67</v>
       </c>
       <c r="W4" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z4" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AD4" t="n">
         <v>1.65</v>
@@ -1097,10 +1097,10 @@
         <v>1.25</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AG4" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="O5" t="n">
-        <v>3.35</v>
+        <v>3.56</v>
       </c>
       <c r="P5" t="n">
-        <v>6.17</v>
+        <v>4.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
         <v>2.08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T5" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U5" t="n">
-        <v>3.08</v>
+        <v>2.73</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.8</v>
+        <v>3.48</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.13</v>
+        <v>1.9</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="O6" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="P6" t="n">
         <v>3.1</v>
@@ -1382,31 +1382,31 @@
         <v>2.88</v>
       </c>
       <c r="U6" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="V6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
         <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AD6" t="n">
         <v>1.29</v>
@@ -1415,10 +1415,10 @@
         <v>1.07</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="O7" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="P7" t="n">
-        <v>5</v>
+        <v>3.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="R7" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="S7" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="T7" t="n">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="U7" t="n">
-        <v>3.78</v>
+        <v>3.42</v>
       </c>
       <c r="V7" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="W7" t="n">
         <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AB7" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z7" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AC7" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.31</v>
+        <v>2.09</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.04</v>
+        <v>1.84</v>
       </c>
       <c r="O8" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="S8" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="T8" t="n">
-        <v>2.21</v>
+        <v>2.34</v>
       </c>
       <c r="U8" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="V8" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="AC8" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
